--- a/artfynd/A 20132-2025 artfynd.xlsx
+++ b/artfynd/A 20132-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107422423</v>
+        <v>136820741</v>
       </c>
       <c r="B5" t="n">
-        <v>93215</v>
+        <v>93421</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,34 +997,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+          <t>Börtnan, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>440862</v>
+        <v>440771</v>
       </c>
       <c r="R5" t="n">
-        <v>6951803</v>
+        <v>6951981</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1055,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-10-30</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1071,16 +1085,118 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Maria Edstam</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136820741</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>107422423</v>
+      </c>
+      <c r="B6" t="n">
+        <v>93215</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>4368</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Dofttaggsvamp</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hydnellum suaveolens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Scop.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sydväst om Flåsjön och Börtnan, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>440862</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6951803</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vemdalen</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-07-01</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-10-30</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/107422423</t>
         </is>
@@ -1092,6 +1208,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20132-2025 artfynd.xlsx
+++ b/artfynd/A 20132-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136820741</v>
       </c>
       <c r="B5" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20132-2025 artfynd.xlsx
+++ b/artfynd/A 20132-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136820741</v>
       </c>
       <c r="B5" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20132-2025 artfynd.xlsx
+++ b/artfynd/A 20132-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136820741</v>
       </c>
       <c r="B5" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20132-2025 artfynd.xlsx
+++ b/artfynd/A 20132-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136820741</v>
       </c>
       <c r="B5" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20132-2025 artfynd.xlsx
+++ b/artfynd/A 20132-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136820741</v>
       </c>
       <c r="B5" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20132-2025 artfynd.xlsx
+++ b/artfynd/A 20132-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136820741</v>
       </c>
       <c r="B5" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20132-2025 artfynd.xlsx
+++ b/artfynd/A 20132-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136820741</v>
       </c>
       <c r="B5" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20132-2025 artfynd.xlsx
+++ b/artfynd/A 20132-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136820741</v>
       </c>
       <c r="B5" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20132-2025 artfynd.xlsx
+++ b/artfynd/A 20132-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136820741</v>
       </c>
       <c r="B5" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20132-2025 artfynd.xlsx
+++ b/artfynd/A 20132-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136820741</v>
       </c>
       <c r="B5" t="n">
-        <v>93454</v>
+        <v>93457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20132-2025 artfynd.xlsx
+++ b/artfynd/A 20132-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136820741</v>
       </c>
       <c r="B5" t="n">
-        <v>93457</v>
+        <v>93467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20132-2025 artfynd.xlsx
+++ b/artfynd/A 20132-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136820741</v>
       </c>
       <c r="B5" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20132-2025 artfynd.xlsx
+++ b/artfynd/A 20132-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136820741</v>
       </c>
       <c r="B5" t="n">
-        <v>93468</v>
+        <v>93473</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20132-2025 artfynd.xlsx
+++ b/artfynd/A 20132-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136820741</v>
       </c>
       <c r="B5" t="n">
-        <v>93473</v>
+        <v>93475</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20132-2025 artfynd.xlsx
+++ b/artfynd/A 20132-2025 artfynd.xlsx
@@ -989,7 +989,7 @@
         <v>136820741</v>
       </c>
       <c r="B5" t="n">
-        <v>93475</v>
+        <v>93481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
